--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487451_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487451_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.6094</v>
+        <v>6.0328</v>
       </c>
       <c r="E2" t="n">
-        <v>8.316800000000001</v>
+        <v>6.9006</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.7075</v>
+        <v>-0.8679</v>
       </c>
       <c r="G2" t="n">
         <v>1.2809</v>
@@ -610,13 +610,13 @@
         <v>0.3917</v>
       </c>
       <c r="S2" t="n">
-        <v>3.1808</v>
+        <v>1.6041</v>
       </c>
       <c r="T2" t="n">
-        <v>2.1702</v>
+        <v>0.754</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0105</v>
+        <v>0.8502</v>
       </c>
       <c r="V2" t="n">
         <v>2.9519</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.7288</v>
+        <v>2.5302</v>
       </c>
       <c r="E3" t="n">
-        <v>4.2042</v>
+        <v>3.2997</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4754</v>
+        <v>-0.7695</v>
       </c>
       <c r="G3" t="n">
         <v>1.5601</v>
@@ -688,13 +688,13 @@
         <v>0.7834</v>
       </c>
       <c r="S3" t="n">
-        <v>1.9936</v>
+        <v>0.795</v>
       </c>
       <c r="T3" t="n">
-        <v>1.4286</v>
+        <v>0.524</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.271</v>
       </c>
       <c r="V3" t="n">
         <v>-0.6083</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3956</v>
+        <v>0.3214</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.15</v>
+        <v>-0.0906</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5456</v>
+        <v>0.412</v>
       </c>
       <c r="G4" t="n">
         <v>0.2648</v>
@@ -766,13 +766,13 @@
         <v>0.3917</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7184</v>
+        <v>0.6442</v>
       </c>
       <c r="T4" t="n">
-        <v>0.09470000000000001</v>
+        <v>0.1541</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6237</v>
+        <v>0.4901</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.2785</v>
+        <v>-0.5468</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.6549</v>
+        <v>-0.1103</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6237</v>
+        <v>-0.4365</v>
       </c>
       <c r="G5" t="n">
         <v>-0.0539</v>
@@ -844,13 +844,13 @@
         <v>0.9792</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6288</v>
+        <v>1.3605</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2923</v>
+        <v>0.2523</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9211</v>
+        <v>1.1082</v>
       </c>
       <c r="V5" t="n">
         <v>0.3009</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. FERNANDEZ ALVAREZ</t>
+          <t>G. RODRIGUEZ LUQUE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.8277</v>
+        <v>-1.8616</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9987</v>
+        <v>0.71</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.829</v>
+        <v>-2.5716</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.0058</v>
+        <v>0.5975</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.4151</v>
+        <v>1.2601</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4093</v>
+        <v>-0.6626</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.6006</v>
+        <v>2.4058</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6006</v>
+        <v>3.2256</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-0.8198</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4052</v>
+        <v>-1.8083</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8145</v>
+        <v>-1.9655</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4093</v>
+        <v>0.1572</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.9792</v>
+        <v>-2.546</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9792</v>
+        <v>-3.1336</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>0.5875</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3739</v>
+        <v>1.1178</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5810999999999999</v>
+        <v>0.2788</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2072</v>
+        <v>0.839</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.2166</v>
+        <v>-1.0309</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.159</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2166</v>
+        <v>-2.1899</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. RODRIGUEZ LUQUE</t>
+          <t>S. SHARASHIDZE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.848</v>
+        <v>-2.4285</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3298</v>
+        <v>1.7375</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.5182</v>
+        <v>-4.166</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5975</v>
+        <v>-0.8138</v>
       </c>
       <c r="H7" t="n">
-        <v>1.2601</v>
+        <v>-2.6377</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6626</v>
+        <v>1.8239</v>
       </c>
       <c r="J7" t="n">
-        <v>2.4058</v>
+        <v>1.8204</v>
       </c>
       <c r="K7" t="n">
-        <v>3.2256</v>
+        <v>-0.1244</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.8198</v>
+        <v>1.9447</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.8083</v>
+        <v>-2.6342</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.9655</v>
+        <v>-2.5134</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1572</v>
+        <v>-0.1209</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.546</v>
+        <v>-1.5668</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.1336</v>
+        <v>-2.1543</v>
       </c>
       <c r="R7" t="n">
         <v>0.5875</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1314</v>
+        <v>-0.3488</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7611</v>
+        <v>-0.3617</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8924</v>
+        <v>0.0129</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.0309</v>
+        <v>0.3009</v>
       </c>
       <c r="W7" t="n">
-        <v>1.159</v>
+        <v>2.4332</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.1899</v>
+        <v>-2.1323</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. SHARASHIDZE</t>
+          <t>C. FERNANDEZ ALVAREZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.3322</v>
+        <v>-3.1615</v>
       </c>
       <c r="E8" t="n">
-        <v>1.0477</v>
+        <v>-1.3058</v>
       </c>
       <c r="F8" t="n">
-        <v>-4.3799</v>
+        <v>-1.8557</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.8138</v>
+        <v>-1.0058</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.6377</v>
+        <v>-1.4151</v>
       </c>
       <c r="I8" t="n">
-        <v>1.8239</v>
+        <v>0.4093</v>
       </c>
       <c r="J8" t="n">
-        <v>1.8204</v>
+        <v>-0.6006</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.1244</v>
+        <v>-0.6006</v>
       </c>
       <c r="L8" t="n">
-        <v>1.9447</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.6342</v>
+        <v>-0.4052</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.5134</v>
+        <v>-0.8145</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1209</v>
+        <v>0.4093</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.5668</v>
+        <v>-0.9792</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.1543</v>
+        <v>-0.9792</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5875</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.2525</v>
+        <v>0.0401</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.0516</v>
+        <v>0.2741</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2009</v>
+        <v>-0.2339</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3009</v>
+        <v>-1.2166</v>
       </c>
       <c r="W8" t="n">
-        <v>2.4332</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.1323</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="9">
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.8604</v>
+        <v>-3.187</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.0826</v>
+        <v>-1.4092</v>
       </c>
       <c r="F9" t="n">
         <v>-1.7778</v>
@@ -1156,10 +1156,10 @@
         <v>0.5875</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5523</v>
+        <v>1.2257</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1847</v>
+        <v>0.4887</v>
       </c>
       <c r="U9" t="n">
         <v>0.7369</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.917</v>
+        <v>-6.2714</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.6548</v>
+        <v>-5.1695</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.2622</v>
+        <v>-1.1018</v>
       </c>
       <c r="G10" t="n">
         <v>-5.306</v>
@@ -1234,13 +1234,13 @@
         <v>0.7834</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4453</v>
+        <v>0.2003</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5893</v>
+        <v>-0.1041</v>
       </c>
       <c r="U10" t="n">
-        <v>0.144</v>
+        <v>0.3044</v>
       </c>
       <c r="V10" t="n">
         <v>1.1846</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-9.329999999999998</v>
+        <v>-8.572400000000002</v>
       </c>
       <c r="E11" t="n">
-        <v>3.697900000000002</v>
+        <v>4.562399999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>-13.0281</v>
+        <v>-13.1348</v>
       </c>
       <c r="G11" t="n">
         <v>-4.1803</v>
@@ -1282,7 +1282,7 @@
         <v>-4.4569</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2766</v>
+        <v>0.2766000000000002</v>
       </c>
       <c r="J11" t="n">
         <v>6.765000000000001</v>
@@ -1312,16 +1312,16 @@
         <v>5.091900000000001</v>
       </c>
       <c r="S11" t="n">
-        <v>5.881400000000001</v>
+        <v>6.6389</v>
       </c>
       <c r="T11" t="n">
-        <v>1.3956</v>
+        <v>2.2602</v>
       </c>
       <c r="U11" t="n">
-        <v>4.4855</v>
+        <v>4.3788</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.434399999999999</v>
+        <v>-1.4344</v>
       </c>
       <c r="W11" t="n">
         <v>10.226</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.7305</v>
+        <v>5.9991</v>
       </c>
       <c r="E12" t="n">
-        <v>5.3193</v>
+        <v>5.831</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5888</v>
+        <v>0.1681</v>
       </c>
       <c r="G12" t="n">
         <v>5.9223</v>
@@ -1390,13 +1390,13 @@
         <v>2.9377</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.4749</v>
+        <v>-1.2064</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.7644</v>
+        <v>-1.2527</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7105</v>
+        <v>0.0463</v>
       </c>
       <c r="V12" t="n">
         <v>1.2832</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>O. KOUROUMA</t>
+          <t>R. CHOITHRAMANI BLANCO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.3632</v>
+        <v>4.6775</v>
       </c>
       <c r="E13" t="n">
-        <v>2.7565</v>
+        <v>5.6137</v>
       </c>
       <c r="F13" t="n">
-        <v>1.6066</v>
+        <v>-0.9362</v>
       </c>
       <c r="G13" t="n">
-        <v>3.432</v>
+        <v>0.1666</v>
       </c>
       <c r="H13" t="n">
-        <v>2.4261</v>
+        <v>0.2675</v>
       </c>
       <c r="I13" t="n">
-        <v>1.0059</v>
+        <v>-0.1009</v>
       </c>
       <c r="J13" t="n">
-        <v>2.4613</v>
+        <v>1.4947</v>
       </c>
       <c r="K13" t="n">
-        <v>2.4209</v>
+        <v>2.1673</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0404</v>
+        <v>-0.6726</v>
       </c>
       <c r="M13" t="n">
-        <v>0.9707</v>
+        <v>-1.3281</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0052</v>
+        <v>-1.8999</v>
       </c>
       <c r="O13" t="n">
-        <v>0.9655</v>
+        <v>0.5717</v>
       </c>
       <c r="P13" t="n">
-        <v>1.1751</v>
+        <v>2.7419</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.1751</v>
+        <v>2.7419</v>
       </c>
       <c r="S13" t="n">
-        <v>1.5144</v>
+        <v>-1.0062</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2952</v>
+        <v>-1.0228</v>
       </c>
       <c r="U13" t="n">
-        <v>1.2192</v>
+        <v>0.0166</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.7583</v>
+        <v>2.7752</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>5.1418</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.7583</v>
+        <v>-2.3666</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R. CHOITHRAMANI BLANCO</t>
+          <t>O. KOUROUMA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.2949</v>
+        <v>3.5732</v>
       </c>
       <c r="E14" t="n">
-        <v>5.6137</v>
+        <v>2.1425</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.3188</v>
+        <v>1.4307</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1666</v>
+        <v>3.432</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2675</v>
+        <v>2.4261</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1009</v>
+        <v>1.0059</v>
       </c>
       <c r="J14" t="n">
-        <v>1.4947</v>
+        <v>2.4613</v>
       </c>
       <c r="K14" t="n">
-        <v>2.1673</v>
+        <v>2.4209</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.6726</v>
+        <v>0.0404</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.3281</v>
+        <v>0.9707</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.8999</v>
+        <v>0.0052</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5717</v>
+        <v>0.9655</v>
       </c>
       <c r="P14" t="n">
-        <v>2.7419</v>
+        <v>1.1751</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.7419</v>
+        <v>1.1751</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.3888</v>
+        <v>0.7244</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.0228</v>
+        <v>-0.3188</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.366</v>
+        <v>1.0432</v>
       </c>
       <c r="V14" t="n">
-        <v>2.7752</v>
+        <v>-1.7583</v>
       </c>
       <c r="W14" t="n">
-        <v>5.1418</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.3666</v>
+        <v>-1.7583</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5733</v>
+        <v>2.7541</v>
       </c>
       <c r="E15" t="n">
-        <v>3.0774</v>
+        <v>3.2821</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5041</v>
+        <v>-0.528</v>
       </c>
       <c r="G15" t="n">
         <v>2.0686</v>
@@ -1624,13 +1624,13 @@
         <v>1.5668</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0828</v>
+        <v>0.0979</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5764</v>
+        <v>-0.3717</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4936</v>
+        <v>0.4696</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L. MC-CARTHY SANTOS</t>
+          <t>A. GARRIDO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.458</v>
+        <v>-0.2216</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.2254</v>
+        <v>-1.139</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2326</v>
+        <v>0.9174</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.6301</v>
+        <v>-2.5559</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.5504</v>
+        <v>-0.0646</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9203</v>
+        <v>-2.4913</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.728</v>
+        <v>-0.8236</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.8088</v>
+        <v>1.2895</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0808</v>
+        <v>-2.1131</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0978</v>
+        <v>-1.7323</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7416</v>
+        <v>-1.3541</v>
       </c>
       <c r="O16" t="n">
-        <v>0.8394</v>
+        <v>-0.3782</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9792</v>
+        <v>1.5668</v>
       </c>
       <c r="Q16" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9585</v>
+        <v>2.546</v>
       </c>
       <c r="S16" t="n">
-        <v>1.4005</v>
+        <v>-0.791</v>
       </c>
       <c r="T16" t="n">
-        <v>1.3803</v>
+        <v>-0.8280999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0201</v>
+        <v>0.0371</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.2076</v>
+        <v>1.5586</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1014</v>
+        <v>1.492</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.309</v>
+        <v>0.06660000000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. GARRIDO RODRIGUEZ</t>
+          <t>L. MC-CARTHY SANTOS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.0183</v>
+        <v>-1.403</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.8553</v>
+        <v>-1.5558</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.163</v>
+        <v>0.1528</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.5559</v>
+        <v>-1.6301</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0646</v>
+        <v>-2.5504</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.4913</v>
+        <v>0.9203</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.8236</v>
+        <v>-1.728</v>
       </c>
       <c r="K17" t="n">
-        <v>1.2895</v>
+        <v>-1.8088</v>
       </c>
       <c r="L17" t="n">
-        <v>-2.1131</v>
+        <v>0.0808</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.7323</v>
+        <v>0.0978</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.3541</v>
+        <v>-0.7416</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3782</v>
+        <v>0.8394</v>
       </c>
       <c r="P17" t="n">
-        <v>1.5668</v>
+        <v>0.9792</v>
       </c>
       <c r="Q17" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R17" t="n">
-        <v>2.546</v>
+        <v>1.9585</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.5878</v>
+        <v>0.4555</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.5445</v>
+        <v>0.05</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.0433</v>
+        <v>0.4055</v>
       </c>
       <c r="V17" t="n">
-        <v>1.5586</v>
+        <v>-1.2076</v>
       </c>
       <c r="W17" t="n">
-        <v>1.492</v>
+        <v>1.1014</v>
       </c>
       <c r="X17" t="n">
-        <v>0.06660000000000001</v>
+        <v>-2.309</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.7075</v>
+        <v>-2.8723</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.4849</v>
+        <v>-0.9732</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.2226</v>
+        <v>-1.899</v>
       </c>
       <c r="G18" t="n">
         <v>-2.5915</v>
@@ -1858,13 +1858,13 @@
         <v>1.7626</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.662</v>
+        <v>-0.8268</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.111</v>
+        <v>-0.5993000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.551</v>
+        <v>-0.2275</v>
       </c>
       <c r="V18" t="n">
         <v>-1.2166</v>
@@ -1891,22 +1891,22 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>9.7781</v>
+        <v>12.507</v>
       </c>
       <c r="E19" t="n">
         <v>13.2013</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.4233</v>
+        <v>-0.6941999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>4.812000000000001</v>
+        <v>4.811999999999999</v>
       </c>
       <c r="H19" t="n">
         <v>5.442400000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6303999999999997</v>
+        <v>-0.6303999999999998</v>
       </c>
       <c r="J19" t="n">
         <v>11.7599</v>
@@ -1936,13 +1936,13 @@
         <v>14.6886</v>
       </c>
       <c r="S19" t="n">
-        <v>-5.2814</v>
+        <v>-2.5526</v>
       </c>
       <c r="T19" t="n">
-        <v>-4.343599999999999</v>
+        <v>-4.343400000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.9378999999999998</v>
+        <v>1.7908</v>
       </c>
       <c r="V19" t="n">
         <v>1.4345</v>
